--- a/analytics/ueq_results.xlsx
+++ b/analytics/ueq_results.xlsx
@@ -747,7 +747,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>attractive_unattractive</t>
+          <t>meets_expectations_does_not_meet_expectations</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -757,7 +757,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>meets_expectations_does_not_meet_expectations</t>
+          <t>attractive_unattractive</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -777,7 +777,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>friendly_unfriendly</t>
+          <t>good_bad</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -787,7 +787,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>good_bad</t>
+          <t>friendly_unfriendly</t>
         </is>
       </c>
       <c r="B23" t="n">
